--- a/modeller/Use Case.xlsx
+++ b/modeller/Use Case.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Datamatiker\Projekter\Hydac\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frede\git\HYDAC\Modeller\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB5BB8D8-FF5E-4456-B0A0-90F19AFBD58E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0DA9E23-82E8-4289-84FF-324E25760103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="561" xr2:uid="{FAE73960-6D5B-49EE-8D5E-7E75CD0D9398}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="52">
   <si>
     <t>Primær aktør</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Medarbejder</t>
   </si>
   <si>
-    <t>1. Medarbejder møder ind om morgnen</t>
-  </si>
-  <si>
     <t>2. Medarbejder går hen til skærmen</t>
   </si>
   <si>
@@ -80,30 +77,12 @@
     <t>5. Medarbejder trykker "Ankomst"</t>
   </si>
   <si>
-    <t>6. Medarbejder vælger smiley efter humør, rød gul grøn, eller blank</t>
-  </si>
-  <si>
-    <t>7. System melder "God dag"</t>
-  </si>
-  <si>
     <t>UC2</t>
   </si>
   <si>
     <t>1. Medarbejder går hen til skærmen</t>
   </si>
   <si>
-    <t>8. Medarbejderens dag er slut</t>
-  </si>
-  <si>
-    <t>Gentage trin 2-4</t>
-  </si>
-  <si>
-    <t>9. Medarbejder trykker "Afgang"</t>
-  </si>
-  <si>
-    <t>10. Systemet skriver "God dag" og timerne bliver registreret til lønafdelingen</t>
-  </si>
-  <si>
     <t>Medarbejder booker møde med kunde</t>
   </si>
   <si>
@@ -146,15 +125,6 @@
     <t xml:space="preserve">Medarbejder </t>
   </si>
   <si>
-    <t>Tjek ind og ud</t>
-  </si>
-  <si>
-    <t>Tjekker ind om morgenen, og ud efter arbejde</t>
-  </si>
-  <si>
-    <t>Registrere sin ankomst, og melde sin afgang</t>
-  </si>
-  <si>
     <t>Besøgende</t>
   </si>
   <si>
@@ -186,6 +156,45 @@
   </si>
   <si>
     <t>8. Systemet giver reception? Besked, og ansvarlige for møde bliver advaret.</t>
+  </si>
+  <si>
+    <t>Tjekker ud efter arbejde</t>
+  </si>
+  <si>
+    <t>Tjek ud</t>
+  </si>
+  <si>
+    <t>UC4</t>
+  </si>
+  <si>
+    <t>Melder sin afgang</t>
+  </si>
+  <si>
+    <t>1. Medarbejderens dag er slut.</t>
+  </si>
+  <si>
+    <t>5. Medarbejder trykker "Afgang"</t>
+  </si>
+  <si>
+    <t>6. System melder "God dag"</t>
+  </si>
+  <si>
+    <t>Tjekker ind om morgenen</t>
+  </si>
+  <si>
+    <t>1. Medarbejder møder ind om morgenen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tjek ind </t>
+  </si>
+  <si>
+    <t>Registrere sin ankomst</t>
+  </si>
+  <si>
+    <t>6. Medarbejder vælger smiley efter humør, rød, gul, grøn, eller blank</t>
+  </si>
+  <si>
+    <t>7. System melder "*Ankomst registreret*"</t>
   </si>
 </sst>
 </file>
@@ -221,7 +230,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -229,18 +238,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39673B22-004F-4717-8A37-72698BEC2F7D}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15.265625" bestFit="1" customWidth="1"/>
@@ -584,263 +624,328 @@
     <col min="5" max="5" width="63.73046875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="63.73046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="54.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="3"/>
+      <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="E1" s="3"/>
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
+      <c r="H1" s="3"/>
+      <c r="J1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="3"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="G5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A8" s="1"/>
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="J8" s="1"/>
+      <c r="K8" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A9" s="1"/>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A10" s="1"/>
+      <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="J11" s="1"/>
+      <c r="K11" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A12" s="1"/>
+      <c r="B12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A13" s="1"/>
+      <c r="B13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A14" s="1"/>
+      <c r="B14" s="2"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14" s="4"/>
-      <c r="B14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A15" s="4"/>
-      <c r="B15" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A16" s="4"/>
-      <c r="B16" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17" s="4"/>
-      <c r="B17" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A15" s="1"/>
+      <c r="B15" s="2"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A16" s="1"/>
+      <c r="B16" s="2"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A17" s="1"/>
+      <c r="B17" s="2"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/modeller/Use Case.xlsx
+++ b/modeller/Use Case.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="Denne_projektmappe" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frede\git\HYDAC\Modeller\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Hydac\HYDAC\modeller\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0DA9E23-82E8-4289-84FF-324E25760103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F4BBCF-75D7-4625-B143-AFB7C937B253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="561" xr2:uid="{FAE73960-6D5B-49EE-8D5E-7E75CD0D9398}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="561" xr2:uid="{FAE73960-6D5B-49EE-8D5E-7E75CD0D9398}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="60">
   <si>
     <t>Primær aktør</t>
   </si>
@@ -158,27 +158,12 @@
     <t>8. Systemet giver reception? Besked, og ansvarlige for møde bliver advaret.</t>
   </si>
   <si>
-    <t>Tjekker ud efter arbejde</t>
-  </si>
-  <si>
     <t>Tjek ud</t>
   </si>
   <si>
     <t>UC4</t>
   </si>
   <si>
-    <t>Melder sin afgang</t>
-  </si>
-  <si>
-    <t>1. Medarbejderens dag er slut.</t>
-  </si>
-  <si>
-    <t>5. Medarbejder trykker "Afgang"</t>
-  </si>
-  <si>
-    <t>6. System melder "God dag"</t>
-  </si>
-  <si>
     <t>Tjekker ind om morgenen</t>
   </si>
   <si>
@@ -195,14 +180,61 @@
   </si>
   <si>
     <t>7. System melder "*Ankomst registreret*"</t>
+  </si>
+  <si>
+    <t>Tjek ud efter arbejde</t>
+  </si>
+  <si>
+    <t>Melde sin afgang</t>
+  </si>
+  <si>
+    <t>1. Medarbejderens dag er slut</t>
+  </si>
+  <si>
+    <t>2. Medarbejder trykker "Medarbejder"</t>
+  </si>
+  <si>
+    <t>3. Medarbejder indtaster sit personlige 4-cifret medarbejder nummer</t>
+  </si>
+  <si>
+    <t>4. Medarbejder trykker "Afgang"</t>
+  </si>
+  <si>
+    <t>5. Systemet skriver "God dag" og timerne bliver registreret til lønafdelingen</t>
+  </si>
+  <si>
+    <t>Kolonne2</t>
+  </si>
+  <si>
+    <t>Use Case Nummer:</t>
+  </si>
+  <si>
+    <t>Use Case navn:</t>
+  </si>
+  <si>
+    <t>Primær aktør:</t>
+  </si>
+  <si>
+    <t>Handling:</t>
+  </si>
+  <si>
+    <t>Mål:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -230,7 +262,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -239,9 +271,242 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -254,33 +519,116 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -615,338 +963,335 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39673B22-004F-4717-8A37-72698BEC2F7D}">
-  <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetPr codeName="Ark1"/>
+  <dimension ref="A1:H30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="59.53125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="63.73046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="63.73046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="54.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="62" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="67.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="62.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="D1" s="3" t="s">
+      <c r="B1" s="29"/>
+      <c r="D1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="G1" s="3" t="s">
+      <c r="E1" s="25"/>
+      <c r="G1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3"/>
-      <c r="J1" s="3" t="s">
+      <c r="H1" s="25"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="34"/>
+      <c r="B8" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="36"/>
+      <c r="B9" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="6"/>
+      <c r="H9" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="36"/>
+      <c r="B10" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="6"/>
+      <c r="H10" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="36"/>
+      <c r="B11" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="36"/>
+      <c r="B12" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="H12" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="37"/>
+      <c r="B13" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="6"/>
+      <c r="H13" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D14" s="7"/>
+      <c r="E14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="7"/>
+      <c r="H14" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="3"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
+      <c r="B20" s="29"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A3" s="1" t="s">
+      <c r="B21" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B22" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="5" t="s">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" s="1"/>
-      <c r="B8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" s="1"/>
-      <c r="K8" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A9" s="1"/>
-      <c r="B9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A10" s="1"/>
-      <c r="B10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10" s="1"/>
-      <c r="K10" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A11" s="1"/>
-      <c r="B11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A12" s="1"/>
-      <c r="B12" s="2" t="s">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J12" s="1"/>
-      <c r="K12" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A13" s="1"/>
-      <c r="B13" s="2" t="s">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J13" s="1"/>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A14" s="1"/>
-      <c r="B14" s="2"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14" s="1"/>
-      <c r="H14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J14" s="1"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A15" s="1"/>
-      <c r="B15" s="2"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A16" s="1"/>
-      <c r="B16" s="2"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A17" s="1"/>
-      <c r="B17" s="2"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="2"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="4"/>
+      <c r="B30" s="15" t="s">
+        <v>53</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A20:B20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/modeller/Use Case.xlsx
+++ b/modeller/Use Case.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="Denne_projektmappe" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Hydac\HYDAC\modeller\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frede\git\HYDAC\Modeller\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F4BBCF-75D7-4625-B143-AFB7C937B253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5FE9302-7273-436D-B426-2D4B68C813BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="561" xr2:uid="{FAE73960-6D5B-49EE-8D5E-7E75CD0D9398}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="16201" windowHeight="9308" tabRatio="561" xr2:uid="{FAE73960-6D5B-49EE-8D5E-7E75CD0D9398}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="59">
   <si>
     <t>Primær aktør</t>
   </si>
@@ -98,9 +98,6 @@
     <t>3. Medarbejder indstaster sit personlige 4-ciftret medarbejder nummer</t>
   </si>
   <si>
-    <t>4. Medarbejder indtaster sit personlige 4-cifret medarbejder nummer</t>
-  </si>
-  <si>
     <t>4. Medarbejder vælger "Book møde"</t>
   </si>
   <si>
@@ -179,9 +176,6 @@
     <t>6. Medarbejder vælger smiley efter humør, rød, gul, grøn, eller blank</t>
   </si>
   <si>
-    <t>7. System melder "*Ankomst registreret*"</t>
-  </si>
-  <si>
     <t>Tjek ud efter arbejde</t>
   </si>
   <si>
@@ -203,9 +197,6 @@
     <t>5. Systemet skriver "God dag" og timerne bliver registreret til lønafdelingen</t>
   </si>
   <si>
-    <t>Kolonne2</t>
-  </si>
-  <si>
     <t>Use Case Nummer:</t>
   </si>
   <si>
@@ -219,6 +210,12 @@
   </si>
   <si>
     <t>Mål:</t>
+  </si>
+  <si>
+    <t>4. Medarbejder indtaster sit personlige 4-cifret medarbejdernummer</t>
+  </si>
+  <si>
+    <t>7. System melder "God dag"</t>
   </si>
 </sst>
 </file>
@@ -581,7 +578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -606,29 +603,25 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -965,37 +958,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39673B22-004F-4717-8A37-72698BEC2F7D}">
   <sheetPr codeName="Ark1"/>
   <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="62" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.1328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="67.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="62.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.1328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="62.1328125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="D1" s="24" t="s">
+      <c r="B1" s="32"/>
+      <c r="D1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="G1" s="24" t="s">
+      <c r="E1" s="34"/>
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="25"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="31" t="s">
+      <c r="H1" s="34"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A2" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="27" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="11" t="s">
@@ -1008,15 +1001,15 @@
         <v>5</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="33" t="s">
-        <v>43</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A3" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>42</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>4</v>
@@ -1028,15 +1021,15 @@
         <v>4</v>
       </c>
       <c r="H3" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A4" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="29" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="33" t="s">
-        <v>27</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>0</v>
@@ -1048,15 +1041,15 @@
         <v>0</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="33" t="s">
-        <v>41</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>40</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>1</v>
@@ -1068,15 +1061,15 @@
         <v>1</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="33" t="s">
-        <v>44</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>43</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>2</v>
@@ -1088,15 +1081,15 @@
         <v>2</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="31" t="s">
-        <v>42</v>
+      <c r="B7" s="27" t="s">
+        <v>41</v>
       </c>
       <c r="D7" s="22" t="s">
         <v>3</v>
@@ -1108,12 +1101,12 @@
         <v>3</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="34"/>
-      <c r="B8" s="35" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A8" s="30"/>
+      <c r="B8" s="14" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="6"/>
@@ -1122,12 +1115,12 @@
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="36"/>
-      <c r="B9" s="35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A9" s="2"/>
+      <c r="B9" s="14" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="6"/>
@@ -1136,152 +1129,152 @@
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="35" t="s">
-        <v>19</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A10" s="2"/>
+      <c r="B10" s="14" t="s">
+        <v>57</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="36"/>
-      <c r="B11" s="35" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A11" s="2"/>
+      <c r="B11" s="14" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="36"/>
-      <c r="B12" s="35" t="s">
-        <v>45</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A12" s="2"/>
+      <c r="B12" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="37"/>
-      <c r="B13" s="38" t="s">
-        <v>46</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="4"/>
+      <c r="B13" s="15" t="s">
+        <v>58</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="D14" s="7"/>
       <c r="E14" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="20" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A20" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="29"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="26" t="s">
+      <c r="B20" s="32"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A21" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="27" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B21" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" s="16" t="s">
         <v>4</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" s="16" t="s">
         <v>0</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" s="16" t="s">
         <v>1</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A25" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A27" s="2"/>
       <c r="B27" s="14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28" s="2"/>
       <c r="B28" s="14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29" s="2"/>
       <c r="B29" s="14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A30" s="4"/>
       <c r="B30" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
